--- a/study/returned/questionnaire_rater2.xlsx
+++ b/study/returned/questionnaire_rater2.xlsx
@@ -4981,7 +4981,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>You should apply through the state admissions centre (the state Tertiary Admissions Centre) as an international student studying Year 12 in Australia. The the state admissions centre code for the Bachelor of Information Technology is 733001. You may also be eligible for Adjustment (previously known as Bonus Points). For more information, visit study.example.edu/information-resources/high-school-students/anon@example.edu</t>
+          <t>You should apply through the state admissions centre (the state Tertiary Admissions Centre) as an international student studying Year 12 in Australia. The state admissions centre code for the Bachelor of Information Technology is 733001. You may also be eligible for Adjustment (previously known as Bonus Points). For more information, visit study.example.edu/information-resources/high-school-students/anon@example.edu</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
@@ -5789,7 +5789,7 @@
 2. **Student Advisers**: Provide confidential support for career development, among other services.
    - Website: &lt;https://my.example.edu/contact/student-central&gt;
 3. **the University CareerHub**: An online platform listing job vacancies, internships, and events tailored to the University students.
-   - Website: &lt;https://uq.careerhub.com.au/&gt;
+   - Website: &lt;https://the University.careerhub.com.au/&gt;
 4. **the University College**: Offers short courses and professional development programs to enhance employability.
    - Website: &lt;https://uqcollege.example.edu/&gt;
 5. **Faculty-specific resources**: The Faculty of Engineering, Architecture and Information Technology (EAIT) has its own career services, including career fairs, workshops, and employer networking events.
@@ -5820,7 +5820,7 @@
           <t>Based on the provided references, the University offers several career services to help IT students find employment:
 1. **Student Central**: This service helps with employability development, including global study, internships, research projects, career workshops, and industry events. (Source: [1], p.81)
 2. **Student Advisers**: The Student Advice Team provides support for career development, among other services. They can help with private appointments and confidential services. (Source: [1])
-3. **The Student Union (UQU)**: UQU can also help with legal or migration support, which could be beneficial for international students seeking employment. (Source: [1])
+3. **The Student Union (the Student Union)**: the Student Union can also help with legal or migration support, which could be beneficial for international students seeking employment. (Source: [1])
 4. **Peer Assisted Study Sessions (PASS)**: While not directly related to career services, PASS can help IT students improve their study habits and coursework, which can indirectly enhance their employability. (Source: [1])
 5. **Industry Events and Careers Evenings**: the University hosts various events like the "the city City Engineering, Design and Computing Careers Evening" where students can network with industry professionals. (Source: [2])
 6. **Alumni Success Stories**: the University shares success stories of IT graduates who have found employment, which can provide</t>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>The the main campus campus library provides academic information resources, welcoming study spaces, a world-class collection, and knowledgeable staff to assist with research and study questions. Online resources and study rooms are also available. More information is at library.example.edu.</t>
+          <t>The main campus library provides academic information resources, welcoming study spaces, a world-class collection, and knowledgeable staff to assist with research and study questions. Online resources and study rooms are also available. More information is at library.example.edu.</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       <c r="B6" s="7" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Okay, so I need to figure out what library services are available to BIT students at the main campus. First, I should clarify what BIT refers to here. BIT could stand for different things, but in the context of a university, it's likely the the city Institute of Technology, which is now part of Griffith University. the main campus is a campus of Griffith University, so I think the user is asking about Griffith University's library services for students enrolled in the Bachelor of Information Technology (BIT) program at the the main campus campus.
+Okay, so I need to figure out what library services are available to BIT students at the main campus. First, I should clarify what BIT refers to here. BIT could stand for different things, but in the context of a university, it's likely the city Institute of Technology, which is now part of Griffith University. the main campus is a campus of Griffith University, so I think the user is asking about Griffith University's library services for students enrolled in the Bachelor of Information Technology (BIT) program at the main campus.
 Alright, so I need to list the library services available to BIT students there. Let me start by recalling what university libraries typically offer. They usually have physical books, e-books, journals, databases, interlibrary loans, study spaces, printing services, research help, workshops, and maybe access to specialized resources for certain disciplines.
 But I should check if Griffith University's library has specific services for BIT students. Let me think. Griffith University's library is called the Griffith University Library, and they have multiple campuses, including the main campus. The library services would be similar across campuses, but maybe there are some specific resources for IT students.
 First, physical resources: books, journals, and multimedia materials related to information technology. Then, electronic resources like e-books</t>
@@ -6456,10 +6456,10 @@
         <is>
           <t>&lt;think&gt;
 Okay, the user is asking about library services available to BIT students at the University the main campus. Let me recall what I know.
-First, the University has the University Library, which offers various services. For BIT students, they might need access to technical resources, study spaces, and research help. The the main campus campus has the main library, which is the University Library. They have study areas, group study rooms, and quiet zones. There's also access to computers, printers, and scanners. 
+First, the University has the University Library, which offers various services. For BIT students, they might need access to technical resources, study spaces, and research help. The main campus has the main library, which is the University Library. They have study areas, group study rooms, and quiet zones. There's also access to computers, printers, and scanners. 
 I should mention the library's website, which is study.example.edu, but wait, the library's main site is library.example.edu. Maybe I should correct that. Also, interlibrary loans, access to databases like IEEE or ACM for IT students, and research support like subject librarians. 
 They might also have workshops on academic writing, referencing, and using library resources. The library has a 24/7 access for some areas, but I need to check if that's accurate. Also, the library has a mobile app for accessing resources on the go. 
-Wait, the user is specifically at the main campus, so I should note that the the main campus campus has the main library building, and there are other libraries on other campuses</t>
+Wait, the user is specifically at the main campus, so I should note that the main campus has the main library building, and there are other libraries on other campuses</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
@@ -6485,7 +6485,7 @@
         <is>
           <t>&lt;think&gt;
 Okay, the user is asking about the library services available to BIT students at the main campus. First, I need to confirm which university they're referring to. the main campus is a campus of the University (the University), so BIT students would be part of the University's Business School. 
-I should start by outlining the main services. The the University Library offers access to physical and digital resources. That includes books, journals, databases, and e-books. Then there's interlibrary loans for materials not available on campus. 
+I should start by outlining the main services. The University Library offers access to physical and digital resources. That includes books, journals, databases, and e-books. Then there's interlibrary loans for materials not available on campus. 
 Next, research support is important. They have research guides, workshops on citation and academic writing, and help with literature reviews. Maybe mention the Research Help Desk or the Researcher Support team.
 Study spaces are another key point. The library has quiet study areas, group study rooms, and collaborative spaces. Also, some areas might have technology like computers, printers, and scanners.
 Digital resources are crucial. Access to databases like JSTOR, ProQuest, and business-specific ones like Emerald Insight. E-books and online journals through platforms like EBSCOhost or SpringerLink. Also, the University Library's online portal, the University ePrints, for accessing theses and research outputs.

--- a/study/returned/questionnaire_rater2.xlsx
+++ b/study/returned/questionnaire_rater2.xlsx
@@ -4641,7 +4641,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>What is INFS2200 and what are its prerequisites?</t>
+          <t>What is INFO2200 and what are its prerequisites?</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>INFS2200 is Relational Database Systems. Prerequisite is INFS1200.</t>
+          <t>INFO2200 is Relational Database Systems. Prerequisite is INFO1200.</t>
         </is>
       </c>
     </row>
@@ -4704,9 +4704,9 @@
       <c r="B6" s="7" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Okay, the user is asking about INFS2200 and its prerequisites. Let me recall what I know about this course. INFS2200 is part of the University Bachelor of Information Technology program. From what I remember, it's a core course, probably related to software development or systems analysis. The prerequisites would be the courses that students need to have completed before enrolling in INFS2200.
-I think the prerequisites for INFS2200 are INFS1200 and INFS1300. INFS1200 is usually an introduction to information systems, covering topics like databases and systems analysis. INFS1300 might be about programming or software development fundamentals. These courses provide the foundational knowledge needed for INFS2200, which likely builds on those concepts.
-Wait, I should double-check to make sure I'm not mixing up the course numbers. Let me think. Yes, INFS2200 is typically a second-year course, so the prerequisites would be first-year courses. INFS1200 and INFS1300 are indeed the common prerequisites. However, I should confirm if there are any other requirements, like a certain GPA</t>
+Okay, the user is asking about INFO2200 and its prerequisites. Let me recall what I know about this course. INFO2200 is part of the University Bachelor of Information Technology program. From what I remember, it's a core course, probably related to software development or systems analysis. The prerequisites would be the courses that students need to have completed before enrolling in INFO2200.
+I think the prerequisites for INFO2200 are INFO1200 and INFO1300. INFO1200 is usually an introduction to information systems, covering topics like databases and systems analysis. INFO1300 might be about programming or software development fundamentals. These courses provide the foundational knowledge needed for INFO2200, which likely builds on those concepts.
+Wait, I should double-check to make sure I'm not mixing up the course numbers. Let me think. Yes, INFO2200 is typically a second-year course, so the prerequisites would be first-year courses. INFO1200 and INFO1300 are indeed the common prerequisites. However, I should confirm if there are any other requirements, like a certain GPA</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -4730,8 +4730,8 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>INFS2200 is called **Database Systems**. It covers database design, implementation, and management using relational database systems.
-Its prerequisite is **INFS1100 Introduction to IT Systems**.
+          <t>INFO2200 is called **Database Systems**. It covers database design, implementation, and management using relational database systems.
+Its prerequisite is **INFO1100 Introduction to IT Systems**.
 For the most up-to-date and detailed information, please refer to the official program handbook: study.example.edu.</t>
         </is>
       </c>
@@ -4756,14 +4756,14 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>INFS2200 is a course offered at the University of New South Wales (UNSW) in Australia, and it's part of the Bachelor of Information Systems degree. Here's a brief overview of the course and its prerequisites:
+          <t>INFO2200 is a course offered at the University of New South Wales (UNSW) in Australia, and it's part of the Bachelor of Information Systems degree. Here's a brief overview of the course and its prerequisites:
 **Course Title:** Information Systems Analysis and Design
-**Course Code:** INFS2200
+**Course Code:** INFO2200
 **Course Description:** This course introduces students to the analysis and design of information systems. It covers the systematic analysis of business processes and the design of information systems to support those processes. Students will learn how to model business processes, gather and document requirements, and design database systems and user interfaces.
 **Prerequisites:**
-1. **INFS1101 - Introduction to Information Systems:** This is a first-year course that provides an introduction to the field of information systems, including the role of information systems in organizations, the systems development life cycle, and basic database concepts.
+1. **INFO1101 - Introduction to Information Systems:** This is a first-year course that provides an introduction to the field of information systems, including the role of information systems in organizations, the systems development life cycle, and basic database concepts.
 2. **MATH1011 - Mathematics for Business and Economics 1:** This is a first-year mathematics course that covers basic mathematical concepts and techniques relevant to business and economics. It's a prerequisite to ensure students have the necessary mathematical foundation for the course.
-So, to enroll in INFS2200, you would typically need</t>
+So, to enroll in INFO2200, you would typically need</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
@@ -4787,10 +4787,10 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>INFS2200 is a second-year course offered as part of the Bachelor of Information Technology program at the University. The course is titled "Data Structures and Algorithms" and focuses on the design and analysis of efficient algorithms and data structures, which are fundamental to computer science and software engineering.
-The prerequisites for INFS2200 are:
-1. **MATH1071 - Discrete Mathematics**: This course provides the mathematical foundation required for understanding the concepts taught in INFS2200.
-2. **COMP1500 - Programming Fundamentals**: This course ensures students have a solid understanding of programming concepts and skills, which are essential for implementing the algorithms and data structures discussed in INFS2200.
+          <t>INFO2200 is a second-year course offered as part of the Bachelor of Information Technology program at the University. The course is titled "Data Structures and Algorithms" and focuses on the design and analysis of efficient algorithms and data structures, which are fundamental to computer science and software engineering.
+The prerequisites for INFO2200 are:
+1. **MATH1071 - Discrete Mathematics**: This course provides the mathematical foundation required for understanding the concepts taught in INFO2200.
+2. **CORE1500 - Programming Fundamentals**: This course ensures students have a solid understanding of programming concepts and skills, which are essential for implementing the algorithms and data structures discussed in INFO2200.
 For the most accurate and up-to-date information, I recommend checking the official the University Course and Unit Catalogue: https://www.study.example.edu/course/2200</t>
         </is>
       </c>
@@ -4816,11 +4816,11 @@
       <c r="B10" s="7" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Okay, the user is asking about INFS2200 and its prerequisites. Let me recall what I know about this course. INFS2200 is part of the University Bachelor of Information Technology program. From previous interactions, I remember that it's a core course, likely in the second year.
-Prerequisites for INFS2200 would typically be the first-year courses that provide foundational knowledge. The user might be planning their course sequence, so they need to know what they need to have completed before enrolling. I should check if there are any specific courses required, like INFS1200 or INFS1300, which are common first-year IT courses at the University.
+Okay, the user is asking about INFO2200 and its prerequisites. Let me recall what I know about this course. INFO2200 is part of the University Bachelor of Information Technology program. From previous interactions, I remember that it's a core course, likely in the second year.
+Prerequisites for INFO2200 would typically be the first-year courses that provide foundational knowledge. The user might be planning their course sequence, so they need to know what they need to have completed before enrolling. I should check if there are any specific courses required, like INFO1200 or INFO1300, which are common first-year IT courses at the University.
 Also, I need to make sure I'm not giving outdated information. Since course details can change, it's important to direct the user to the official source. I'll mention that they should check the University course catalog or study.example.edu for the most accurate and up-to-date information on prerequisites and course details. That way, they get the correct info even if there are any changes.
 &lt;/think&gt;
-**INFS2200: Information Systems Development** is a core course in the University Bachelor of Information Technology program.</t>
+**INFO2200: Information Systems Development** is a core course in the University Bachelor of Information Technology program.</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>the University provides career services through the Enhance Your Employability program, including global study, internships, career workshops, research projects, and industry events. The EAIT faculty has industry connections through research partnerships and employer networks relevant to IT careers.</t>
+          <t>the University provides career services through the career-development program, including global study, internships, career workshops, research projects, and industry events. The Faculty has industry connections through research partnerships and employer networks relevant to IT careers.</t>
         </is>
       </c>
     </row>
@@ -5792,8 +5792,8 @@
    - Website: &lt;https://the University.careerhub.com.au/&gt;
 4. **the University College**: Offers short courses and professional development programs to enhance employability.
    - Website: &lt;https://uqcollege.example.edu/&gt;
-5. **Faculty-specific resources**: The Faculty of Engineering, Architecture and Information Technology (EAIT) has its own career services, including career fairs, workshops, and employer networking events.
-   - Website: &lt;https://eait.example.edu/students/careers&gt;</t>
+5. **Faculty-specific resources**: The Faculty of Engineering, Architecture and Information Technology (the Faculty) has its own career services, including career fairs, workshops, and employer networking events.
+   - Website: &lt;https://the Faculty.example.edu/students/careers&gt;</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>A transfer may be possible, depending on which courses you have completed and whether they satisfy BCS entry and credit requirements. Contact the School of EECS or the EAIT faculty for formal academic advice before attempting a transfer, as the process is not automatic.</t>
+          <t>A transfer may be possible, depending on which courses you have completed and whether they satisfy BCS entry and credit requirements. Contact the School of the School or the Faculty for formal academic advice before attempting a transfer, as the process is not automatic.</t>
         </is>
       </c>
     </row>

--- a/study/returned/questionnaire_rater2.xlsx
+++ b/study/returned/questionnaire_rater2.xlsx
@@ -5791,9 +5791,9 @@
 3. **the University CareerHub**: An online platform listing job vacancies, internships, and events tailored to the University students.
    - Website: &lt;https://the University.careerhub.com.au/&gt;
 4. **the University College**: Offers short courses and professional development programs to enhance employability.
-   - Website: &lt;https://uqcollege.example.edu/&gt;
+   - Website: &lt;https://unicollege.example.edu/&gt;
 5. **Faculty-specific resources**: The Faculty of Engineering, Architecture and Information Technology (the Faculty) has its own career services, including career fairs, workshops, and employer networking events.
-   - Website: &lt;https://the Faculty.example.edu/students/careers&gt;</t>
+   - Website: &lt;https://dept.example.edu/students/careers&gt;</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
